--- a/New_Outputs/Table4_Regression_Pooled_Group.xlsx
+++ b/New_Outputs/Table4_Regression_Pooled_Group.xlsx
@@ -26,46 +26,46 @@
     <t xml:space="preserve">Intercept</t>
   </si>
   <si>
-    <t xml:space="preserve">7.768***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.238***</t>
+    <t xml:space="preserve">6.925***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.713***</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">1.233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.463**</t>
+    <t xml:space="preserve">1.287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.617*</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">1.938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602</t>
+    <t xml:space="preserve">1.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.866</t>
   </si>
   <si>
     <t xml:space="preserve">log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.412*</t>
+    <t xml:space="preserve">0.199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126</t>
   </si>
   <si>
     <t xml:space="preserve">Drug group (Tramadol vs Hydrocodone)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.430***</t>
+    <t xml:space="preserve">-0.610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860</t>
   </si>
   <si>
     <t xml:space="preserve">Group x 5-HT4</t>
@@ -74,43 +74,43 @@
     <t xml:space="preserve">--</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.424*</t>
+    <t xml:space="preserve">-3.669*</t>
   </si>
   <si>
     <t xml:space="preserve">Group x 5-HT6</t>
   </si>
   <si>
-    <t xml:space="preserve">5.501*</t>
+    <t xml:space="preserve">5.031*</t>
   </si>
   <si>
     <t xml:space="preserve">Group x log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">-5.779***</t>
+    <t xml:space="preserve">0.127</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
-    <t xml:space="preserve">36</t>
+    <t xml:space="preserve">44</t>
   </si>
   <si>
     <t xml:space="preserve">adj. R2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481</t>
+    <t xml:space="preserve">0.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166</t>
   </si>
   <si>
     <t xml:space="preserve">model p</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0e-04</t>
+    <t xml:space="preserve">0.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
   </si>
 </sst>
 </file>
